--- a/datos/censo/genero.xlsx
+++ b/datos/censo/genero.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3594,146 +3594,6 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Transmasculino</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Transfemenino</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>No binario</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Prefiere no responder/No sabe</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Fuente: Censo de Población y Vivienda 2024 - Instituto Nacional de Estadísticas._x000D_
-Nota: La información utilizada fue procesada bajo los principios de protección y privacidad de los datos de la ley 17.374.</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Fuente: Censo de Población y Vivienda 2024 - Instituto Nacional de Estadísticas._x000D_
-Nota: La información utilizada fue procesada bajo los principios de protección y privacidad de los datos de la ley 17.374.</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Fuente: Censo de Población y Vivienda 2024 - Instituto Nacional de Estadísticas._x000D_
-Nota: La información utilizada fue procesada bajo los principios de protección y privacidad de los datos de la ley 17.374.</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Transmasculino</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Fuente: Censo de Población y Vivienda 2024 - Instituto Nacional de Estadísticas._x000D_
-Nota: La información utilizada fue procesada bajo los principios de protección y privacidad de los datos de la ley 17.374.</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Transfemenino</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Fuente: Censo de Población y Vivienda 2024 - Instituto Nacional de Estadísticas._x000D_
-Nota: La información utilizada fue procesada bajo los principios de protección y privacidad de los datos de la ley 17.374.</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>No binario</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Fuente: Censo de Población y Vivienda 2024 - Instituto Nacional de Estadísticas._x000D_
-Nota: La información utilizada fue procesada bajo los principios de protección y privacidad de los datos de la ley 17.374.</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Otro</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Fuente: Censo de Población y Vivienda 2024 - Instituto Nacional de Estadísticas._x000D_
-Nota: La información utilizada fue procesada bajo los principios de protección y privacidad de los datos de la ley 17.374.</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Prefiere no responder/No sabe</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
